--- a/samples/09_종신보험(암진단포함)_보험료계산.xlsx
+++ b/samples/09_종신보험(암진단포함)_보험료계산.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/500d261d9200e04c/Documents/00 App Project/Life_ins_Doc_Convert_Studio/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7AD84ACAD1DE1D3D74A31BAF28421AD8A18EA06C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_7AD8533A13D80B3C74A31BAF28421AD8A18EA088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,7 +255,7 @@
     <t>10만원당 보험료 (원)</t>
   </si>
   <si>
-    <t>담보 보험료 (원) = 10만원당 × 보장금액/10만</t>
+    <t>담보 보험료 (원) = 10만원당 × 보장금액/10만, 10원 미만 버림</t>
   </si>
   <si>
     <t>P_β 준비금 산출용 순보험료</t>
@@ -264,7 +264,7 @@
     <t>α^공제 해약공제 기준 신계약비</t>
   </si>
   <si>
-    <t>담보 보험료의 합이 이 단위의 보험료입니다. 10만원당 보험료는 담보마다 원 단위로 반올림한 뒤 더합니다.</t>
+    <t>담보 보험료의 합이 이 단위의 보험료입니다. 10만원당 보험료는 담보마다 원 단위로 반올림하고, 담보 보험료는 10원 미만을 버린 뒤 더합니다.</t>
   </si>
 </sst>
 </file>
@@ -4071,11 +4071,11 @@
         <v>68</v>
       </c>
       <c r="BF17" s="4">
-        <f>$BF$16*($BF$6/100000)</f>
+        <f>ROUNDDOWN($BF$16*$BF$6/100000,-1)</f>
         <v>261000</v>
       </c>
       <c r="BG17" s="4">
-        <f>$BG$16*($BG$6/100000)</f>
+        <f>ROUNDDOWN($BG$16*$BG$6/100000,-1)</f>
         <v>81000</v>
       </c>
       <c r="BH17" s="4">
